--- a/public/templates/deck-template.xlsx
+++ b/public/templates/deck-template.xlsx
@@ -799,7 +799,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Energy needed to play it (a whole number). Required.</t>
+          <t>Energy needed to play it (a whole number). Empty counts as 0.</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Its power at a location (a whole number). Required.</t>
+          <t>Its power at a location (a whole number). Empty counts as 0.</t>
         </is>
       </c>
     </row>

--- a/public/templates/deck-template.xlsx
+++ b/public/templates/deck-template.xlsx
@@ -751,7 +751,7 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
